--- a/docs/oc-top-organismos/mobiliario-general-escolar-y-clinico.xlsx
+++ b/docs/oc-top-organismos/mobiliario-general-escolar-y-clinico.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M139"/>
+  <dimension ref="A1:M149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>12669.55</v>
+        <v>12543.1</v>
       </c>
     </row>
     <row r="3">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>79030.36</v>
+        <v>78241.62</v>
       </c>
     </row>
     <row r="4">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>11511.05</v>
+        <v>11448.13</v>
       </c>
     </row>
     <row r="5">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>13172.13</v>
+        <v>13100.13</v>
       </c>
     </row>
     <row r="6">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>19144.72</v>
+        <v>18931.42</v>
       </c>
     </row>
     <row r="7">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>9874.200000000001</v>
+        <v>9764.190000000001</v>
       </c>
     </row>
     <row r="8">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>27350.65</v>
+        <v>27315.84</v>
       </c>
     </row>
     <row r="9">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>11066.61</v>
+        <v>11186.97</v>
       </c>
     </row>
     <row r="10">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>14447.87</v>
+        <v>14605.01</v>
       </c>
     </row>
     <row r="11">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>8609.370000000001</v>
+        <v>8757.98</v>
       </c>
     </row>
     <row r="12">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>6999.47</v>
+        <v>7120.29</v>
       </c>
     </row>
     <row r="13">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>22824.48</v>
+        <v>22982.6</v>
       </c>
     </row>
     <row r="14">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>49853.53</v>
+        <v>50212.95</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>62042.97</v>
+        <v>61932.94</v>
       </c>
     </row>
     <row r="16">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>58336.15</v>
+        <v>58232.68</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1208129-730-CM25</t>
+          <t>1475044-17-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1458,17 +1458,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1488,13 +1488,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>12244.52</v>
+        <v>8239.42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1475044-17-CM25</t>
+          <t>1208129-730-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1519,17 +1519,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>8273.52</v>
+        <v>12194.06</v>
       </c>
     </row>
     <row r="19">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>7569</v>
+        <v>7537.8</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>14803.32</v>
+        <v>14780.37</v>
       </c>
     </row>
     <row r="21">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>13615.3</v>
+        <v>13685.61</v>
       </c>
     </row>
     <row r="22">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>13471.12</v>
+        <v>13296.99</v>
       </c>
     </row>
     <row r="23">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>12139.48</v>
+        <v>11985.28</v>
       </c>
     </row>
     <row r="24">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>13901.65</v>
+        <v>13871.56</v>
       </c>
     </row>
     <row r="25">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>6368.01</v>
+        <v>6362.89</v>
       </c>
     </row>
     <row r="26">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>8845.02</v>
+        <v>8837.91</v>
       </c>
     </row>
     <row r="27">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>13143.96</v>
+        <v>13194.41</v>
       </c>
     </row>
     <row r="28">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>8360.280000000001</v>
+        <v>8382.450000000001</v>
       </c>
     </row>
     <row r="29">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>11137.31</v>
+        <v>11166.84</v>
       </c>
     </row>
     <row r="30">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>8316.879999999999</v>
+        <v>8305.209999999999</v>
       </c>
     </row>
     <row r="31">
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>64016.23</v>
+        <v>64098.29</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1385462-296-CM25</t>
+          <t>1186229-388-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA Y DISTRIBUIDORA LIBERONA S.A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.007.474-8</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>36753.47</v>
+        <v>78484.67999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1495199-3-CM25</t>
+          <t>1495202-3-SE25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2457,20 +2457,24 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>19122</v>
+        <v>16765.18</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1186229-388-CM25</t>
+          <t>1385462-296-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2495,12 +2499,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2510,12 +2514,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA Y DISTRIBUIDORA LIBERONA S.A</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.007.474-8</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2525,13 +2529,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>77948.14999999999</v>
+        <v>37006.46</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1495202-3-SE25</t>
+          <t>1495205-3-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2566,7 +2570,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2579,24 +2583,20 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>16650.57</v>
+        <v>15827.78</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1495205-3-CM25</t>
+          <t>1495199-3-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2651,13 +2651,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>15719.58</v>
+        <v>19253.62</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1495207-5-CM25</t>
+          <t>1495209-4-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2712,13 +2712,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>17732.62</v>
+        <v>13513.51</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1495209-4-CM25</t>
+          <t>1495207-5-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>13421.13</v>
+        <v>17854.68</v>
       </c>
     </row>
     <row r="39">
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>13237.85</v>
+        <v>13328.97</v>
       </c>
     </row>
     <row r="40">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>21179.18</v>
+        <v>21324.96</v>
       </c>
     </row>
     <row r="41">
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>19000.69</v>
+        <v>19131.48</v>
       </c>
     </row>
     <row r="42">
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>27276.81</v>
+        <v>27509.91</v>
       </c>
     </row>
     <row r="43">
@@ -3078,13 +3078,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>37043.46</v>
+        <v>37360.03</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1210674-294-CM25</t>
+          <t>1208107-103-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3119,17 +3119,17 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>BODEGA STOCK SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.744.548-2</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3139,13 +3139,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>58739.57</v>
+        <v>17575.49</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2178-432-CM25</t>
+          <t>1177296-589-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3170,27 +3170,27 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>IMPORTADORA FULLMUEBLES SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.351.814-9</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>7673.64</v>
+        <v>6157.16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1186229-393-CM25</t>
+          <t>2178-432-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3231,27 +3231,27 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>MODUS Design Limitada</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>79.893.240-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3261,13 +3261,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>64254.38</v>
+        <v>7755.95</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1177296-589-CM25</t>
+          <t>1210674-294-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3307,12 +3307,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>IMPORTADORA FULLMUEBLES SPA</t>
+          <t>BODEGA STOCK SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>77.351.814-9</t>
+          <t>76.744.548-2</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3322,13 +3322,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>6091.82</v>
+        <v>59369.64</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1208107-103-CM25</t>
+          <t>1186229-393-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3353,27 +3353,27 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>MODUS Design Limitada</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>79.893.240-3</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>17388.96</v>
+        <v>64943.61</v>
       </c>
     </row>
     <row r="49">
@@ -3444,7 +3444,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>63218.68</v>
+        <v>63564.4</v>
       </c>
     </row>
     <row r="50">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>49009.87</v>
+        <v>49277.9</v>
       </c>
     </row>
     <row r="51">
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>7616.64</v>
+        <v>7507.47</v>
       </c>
     </row>
     <row r="52">
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>8049.98</v>
+        <v>7933.97</v>
       </c>
     </row>
     <row r="53">
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>16065.98</v>
+        <v>16066.08</v>
       </c>
     </row>
     <row r="54">
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>11839.25</v>
+        <v>11855.69</v>
       </c>
     </row>
     <row r="55">
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>27399.77</v>
+        <v>27381.05</v>
       </c>
     </row>
     <row r="56">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>29035.98</v>
+        <v>28936.33</v>
       </c>
     </row>
     <row r="57">
@@ -3932,7 +3932,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>15433.58</v>
+        <v>15380.61</v>
       </c>
     </row>
     <row r="58">
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>7000.93</v>
+        <v>6963.95</v>
       </c>
     </row>
     <row r="59">
@@ -4054,7 +4054,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>51300.07</v>
+        <v>51029.08</v>
       </c>
     </row>
     <row r="60">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>11099.08</v>
+        <v>11029.53</v>
       </c>
     </row>
     <row r="61">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>37550.49</v>
+        <v>37796.6</v>
       </c>
     </row>
     <row r="62">
@@ -4237,13 +4237,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>14928.99</v>
+        <v>15156.27</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5621-6-CM26</t>
+          <t>5153-163-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>92.999.000-5</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4298,13 +4298,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>109064.12</v>
+        <v>58655.43</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5153-163-CM26</t>
+          <t>5647-21-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
+          <t>77.018.060-0</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4359,13 +4359,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>57209.18</v>
+        <v>6886.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5647-21-CM26</t>
+          <t>5621-6-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>6716.9</v>
+        <v>111821.26</v>
       </c>
     </row>
     <row r="66">
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>6708.55</v>
+        <v>6907.95</v>
       </c>
     </row>
     <row r="67">
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>57567.96</v>
+        <v>59279.05</v>
       </c>
     </row>
     <row r="68">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>26529.14</v>
+        <v>26434.69</v>
       </c>
     </row>
     <row r="69">
@@ -4664,13 +4664,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>20487.68</v>
+        <v>20547.03</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1475044-22-CM26</t>
+          <t>5621-56-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4725,13 +4725,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>40524.21</v>
+        <v>6775.1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5621-56-CM26</t>
+          <t>1475044-20-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA Y DISTRIBUIDORA LIBERONA S.A</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.007.474-8</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4786,13 +4786,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>6740.28</v>
+        <v>45222.5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1475044-20-CM26</t>
+          <t>1475044-22-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4832,12 +4832,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA Y DISTRIBUIDORA LIBERONA S.A</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.007.474-8</t>
+          <t>76.028.554-4</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>44990.1</v>
+        <v>40733.54</v>
       </c>
     </row>
     <row r="73">
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>6112.86</v>
+        <v>6168.46</v>
       </c>
     </row>
     <row r="74">
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>9839.450000000001</v>
+        <v>9829.309999999999</v>
       </c>
     </row>
     <row r="75">
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>15396.39</v>
+        <v>15286.09</v>
       </c>
     </row>
     <row r="76">
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>34546.47</v>
+        <v>34495.65</v>
       </c>
     </row>
     <row r="77">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>10846.62</v>
+        <v>10780.71</v>
       </c>
     </row>
     <row r="78">
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>28212.27</v>
+        <v>29458.18</v>
       </c>
     </row>
     <row r="79">
@@ -5274,7 +5274,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>11368.09</v>
+        <v>11396.06</v>
       </c>
     </row>
     <row r="80">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>40493.86</v>
+        <v>40593.49</v>
       </c>
     </row>
     <row r="81">
@@ -5396,7 +5396,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>23054</v>
+        <v>23415.13</v>
       </c>
     </row>
     <row r="82">
@@ -5457,13 +5457,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>9969.780000000001</v>
+        <v>9969.27</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5169-7-CM26</t>
+          <t>1232565-47-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5488,27 +5488,27 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>INTERGROUPE S.A.</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.719.470-6</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5518,13 +5518,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>40921.83</v>
+        <v>8887.66</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1475050-26-CM26</t>
+          <t>1475044-43-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5579,13 +5579,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>30101.05</v>
+        <v>37384.39</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1475044-43-CM26</t>
+          <t>1475050-26-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5640,13 +5640,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>37352.21</v>
+        <v>30126.98</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1232565-47-CM26</t>
+          <t>5169-7-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5671,27 +5671,27 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>INTERGROUPE S.A.</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.719.470-6</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5701,7 +5701,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>8880.01</v>
+        <v>40957.09</v>
       </c>
     </row>
     <row r="87">
@@ -5762,7 +5762,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>6040.89</v>
+        <v>6065.84</v>
       </c>
     </row>
     <row r="88">
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>52194.66</v>
+        <v>52050.69</v>
       </c>
     </row>
     <row r="89">
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>24461.13</v>
+        <v>24178.74</v>
       </c>
     </row>
     <row r="90">
@@ -5945,7 +5945,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>26544.56</v>
+        <v>26063.17</v>
       </c>
     </row>
     <row r="91">
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>11330.62</v>
+        <v>11426.78</v>
       </c>
     </row>
     <row r="92">
@@ -6067,7 +6067,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>18531.92</v>
+        <v>18500.94</v>
       </c>
     </row>
     <row r="93">
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>65320.08</v>
+        <v>65210.86</v>
       </c>
     </row>
     <row r="94">
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>19312.01</v>
+        <v>19549.68</v>
       </c>
     </row>
     <row r="95">
@@ -6250,7 +6250,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>8795.98</v>
+        <v>8913.08</v>
       </c>
     </row>
     <row r="96">
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>65304.87</v>
+        <v>66174.25</v>
       </c>
     </row>
     <row r="97">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>59736.47</v>
+        <v>60531.72</v>
       </c>
     </row>
     <row r="98">
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>13439.56</v>
+        <v>13359.01</v>
       </c>
     </row>
     <row r="99">
@@ -6494,7 +6494,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>9825.18</v>
+        <v>9691.6</v>
       </c>
     </row>
     <row r="100">
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>6523.45</v>
+        <v>6548.16</v>
       </c>
     </row>
     <row r="101">
@@ -6616,13 +6616,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>14656.88</v>
+        <v>14712.41</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5153-829-CM26</t>
+          <t>2177-50-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6647,27 +6647,27 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.018.060-0</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6677,13 +6677,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>23066.26</v>
+        <v>12279.86</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2177-50-CM26</t>
+          <t>5153-829-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6708,27 +6708,27 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6738,13 +6738,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>12310.94</v>
+        <v>23008.02</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1475044-49-CM26</t>
+          <t>2179-102-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6764,32 +6764,32 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>INTERGROUPE S.A.</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>76.719.470-6</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6799,13 +6799,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>14770.58</v>
+        <v>7528.19</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2179-102-CM26</t>
+          <t>1475044-49-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6825,32 +6825,32 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>INTERGROUPE S.A.</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.719.470-6</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>7457.34</v>
+        <v>14910.91</v>
       </c>
     </row>
     <row r="106">
@@ -6921,7 +6921,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>19379.94</v>
+        <v>19186.66</v>
       </c>
     </row>
     <row r="107">
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>9180.18</v>
+        <v>9080.32</v>
       </c>
     </row>
     <row r="108">
@@ -7043,7 +7043,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>18676.77</v>
+        <v>18630.65</v>
       </c>
     </row>
     <row r="109">
@@ -7104,13 +7104,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>28406.58</v>
+        <v>28336.43</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2173-112-CM26</t>
+          <t>2184-150-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7165,13 +7165,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>106544.88</v>
+        <v>16759.3</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2184-150-CM26</t>
+          <t>2173-112-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7226,13 +7226,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>16703.89</v>
+        <v>106898.33</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>5510-54-CM26</t>
+          <t>5510-55-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7287,13 +7287,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>31613.93</v>
+        <v>27411.55</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>5510-55-CM26</t>
+          <t>5510-54-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>27266.56</v>
+        <v>31782.04</v>
       </c>
     </row>
     <row r="114">
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>9753.360000000001</v>
+        <v>9867.77</v>
       </c>
     </row>
     <row r="115">
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>6115.89</v>
+        <v>6178.09</v>
       </c>
     </row>
     <row r="116">
@@ -7531,7 +7531,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>7635.22</v>
+        <v>7577.29</v>
       </c>
     </row>
     <row r="117">
@@ -7592,7 +7592,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>7287.65</v>
+        <v>7320.75</v>
       </c>
     </row>
     <row r="118">
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>57932.17</v>
+        <v>59033.55</v>
       </c>
     </row>
     <row r="119">
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>6770.76</v>
+        <v>6791.69</v>
       </c>
     </row>
     <row r="120">
@@ -7775,7 +7775,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>15232.96</v>
+        <v>15280.06</v>
       </c>
     </row>
     <row r="121">
@@ -7836,13 +7836,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>6593.48</v>
+        <v>6495.8</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2178-186-CM26</t>
+          <t>4794-75-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7862,32 +7862,32 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>INTERGROUPE S.A.</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.719.470-6</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7897,13 +7897,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>22291.54</v>
+        <v>14693.99</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>5586-1964-CM26</t>
+          <t>2178-186-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7923,32 +7923,32 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>INDUMAC LTDA.</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>83.732.700-8</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7958,13 +7958,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>153194.57</v>
+        <v>21833.41</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>4794-75-CM26</t>
+          <t>5586-1964-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7989,27 +7989,27 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>INTERGROUPE S.A.</t>
+          <t>INDUMAC LTDA.</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>76.719.470-6</t>
+          <t>83.732.700-8</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>15002.31</v>
+        <v>150046.15</v>
       </c>
     </row>
     <row r="125">
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>6515.12</v>
+        <v>6540.55</v>
       </c>
     </row>
     <row r="126">
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>9987.85</v>
+        <v>10087.86</v>
       </c>
     </row>
     <row r="127">
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>17052.64</v>
+        <v>17139.53</v>
       </c>
     </row>
     <row r="128">
@@ -8263,13 +8263,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>25467.24</v>
+        <v>25566.37</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>5510-63-CM26</t>
+          <t>5510-64-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8324,13 +8324,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>51102.57</v>
+        <v>54648.37</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>5510-64-CM26</t>
+          <t>5510-63-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8385,13 +8385,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>54532.14</v>
+        <v>51211.49</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>5510-65-CM26</t>
+          <t>5510-66-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8446,13 +8446,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>63067.34</v>
+        <v>38661.76</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>5510-66-CM26</t>
+          <t>5510-65-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8507,7 +8507,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>38411.35</v>
+        <v>63478.5</v>
       </c>
     </row>
     <row r="133">
@@ -8568,7 +8568,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>8655.68</v>
+        <v>8675.530000000001</v>
       </c>
     </row>
     <row r="134">
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>8856.33</v>
+        <v>8918.309999999999</v>
       </c>
     </row>
     <row r="135">
@@ -8690,7 +8690,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>7745.5</v>
+        <v>7728.65</v>
       </c>
     </row>
     <row r="136">
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>200006.3</v>
+        <v>198848.63</v>
       </c>
     </row>
     <row r="137">
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>63550.15</v>
+        <v>63182.31</v>
       </c>
     </row>
     <row r="138">
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>21179.27</v>
+        <v>20839.69</v>
       </c>
     </row>
     <row r="139">
@@ -8934,7 +8934,617 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>39255.8</v>
+        <v>38626.39</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>1232565-213-CM26</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="n">
+        <v>6400.97</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>1232565-216-CM26</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>7106.25</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>5153-1382-CM26</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>STATUS SPA</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>16760.75</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>5416-802-CM26</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="n">
+        <v>9177.83</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>1460278-335-CM26</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>60.911.000-7</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>CHILESEATING</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>76.675.854-1</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="n">
+        <v>10906.78</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>1208983-197-CM26</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="n">
+        <v>17988.57</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>1210674-184-CM26</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>IGMA CONSULTORES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>76.465.697-0</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="n">
+        <v>32898.81</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>5067-1772-CM26</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>60.911.000-7</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>CHILESEATING</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>76.675.854-1</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="n">
+        <v>68935.75999999999</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>507428-878-CM26</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>61.979.210-6</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CHILOE</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>77.749.210-1</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>55525</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>3474-469-CM26</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>61.979.960-7</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="n">
+        <v>11047.36</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-top-organismos/mobiliario-general-escolar-y-clinico.xlsx
+++ b/docs/oc-top-organismos/mobiliario-general-escolar-y-clinico.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M303"/>
+  <dimension ref="A1:M313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1575,7 +1575,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1075956-39-CM25</t>
+          <t>5510-17-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIAL VYB SPA</t>
+          <t>MUEBLES EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.583.479-1</t>
+          <t>79.526.830-8</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1630,13 +1630,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>46802.49</v>
+        <v>48736.32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5510-17-CM25</t>
+          <t>1075956-39-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1656,17 +1656,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MUEBLES EASTON LIMITADA</t>
+          <t>COMERCIAL VYB SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>79.526.830-8</t>
+          <t>76.583.479-1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>48736.32</v>
+        <v>46802.49</v>
       </c>
     </row>
     <row r="21">
@@ -2892,7 +2892,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1079866-301-CM25</t>
+          <t>2177-48-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2912,52 +2912,48 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>65.091.977-7</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>suria ltda</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.827.520-1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>25560.82</v>
+        <v>5805.92</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2177-48-CM25</t>
+          <t>1079866-301-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2977,48 +2973,52 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>65.091.977-7</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>suria ltda</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.827.520-1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>5805.92</v>
+        <v>25560.82</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5153-1186-CM25</t>
+          <t>1079566-171-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3038,42 +3038,46 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.979.370-6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>52898.46</v>
+        <v>14867.29</v>
       </c>
     </row>
     <row r="43">
@@ -3140,7 +3144,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1079566-171-CM25</t>
+          <t>5153-1186-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3160,52 +3164,48 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.979.370-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>92.999.000-5</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>14867.29</v>
+        <v>52898.46</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3453-215-CM25</t>
+          <t>3453-216-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>IGMA CONSULTORES LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.465.697-0</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3264,13 +3264,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>12762.56</v>
+        <v>12429.03</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3453-216-CM25</t>
+          <t>3453-215-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>IGMA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.465.697-0</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3329,7 +3329,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>12429.03</v>
+        <v>12762.56</v>
       </c>
     </row>
     <row r="47">
@@ -3400,7 +3400,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4230-64-CM25</t>
+          <t>2181-114-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3420,48 +3420,52 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>COMERCIAL LLICANCO SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.956.267-2</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>44540.99</v>
+        <v>10562.28</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2181-114-CM25</t>
+          <t>4230-64-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3481,46 +3485,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIAL LLICANCO SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.956.267-2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>10562.28</v>
+        <v>44540.99</v>
       </c>
     </row>
     <row r="50">
@@ -4611,7 +4611,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>507428-3112-CM25</t>
+          <t>507428-3037-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4670,13 +4670,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>7160.27</v>
+        <v>10083.3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>507428-3037-CM25</t>
+          <t>2175-129-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4696,52 +4696,48 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>10083.3</v>
+        <v>8265.98</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2175-129-CM25</t>
+          <t>507428-3111-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4761,48 +4757,52 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>8265.98</v>
+        <v>7160.27</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>507428-3111-CM25</t>
+          <t>507428-3112-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5058,7 +5058,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1696-207-CM25</t>
+          <t>1075956-171-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIALIZADORA MERCADO PUBLICO SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.559.762-5</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5117,13 +5117,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>13916.26</v>
+        <v>6576.46</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1075956-171-CM25</t>
+          <t>1696-207-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5143,32 +5143,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA MERCADO PUBLICO SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.559.762-5</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>6576.46</v>
+        <v>13916.26</v>
       </c>
     </row>
     <row r="76">
@@ -5318,7 +5318,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5153-1570-CM25</t>
+          <t>5153-1578-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5373,13 +5373,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>57742.45</v>
+        <v>56517.15</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5153-1578-CM25</t>
+          <t>2182-100-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5404,43 +5404,47 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>56517.15</v>
+        <v>28416.68</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2182-100-CM25</t>
+          <t>5153-1570-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5465,41 +5469,37 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>92.999.000-5</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>28416.68</v>
+        <v>57742.45</v>
       </c>
     </row>
     <row r="81">
@@ -5761,7 +5761,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5153-1679-CM25</t>
+          <t>5153-1680-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5801,28 +5801,32 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>77.749.210-1</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>11002.25</v>
+        <v>54308.81</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5153-1680-CM25</t>
+          <t>5153-1679-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5862,26 +5866,22 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.749.210-1</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>54308.81</v>
+        <v>11002.25</v>
       </c>
     </row>
     <row r="87">
@@ -6009,7 +6009,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1375158-14-CM25</t>
+          <t>256-1-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6024,22 +6024,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.001.000-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO MEDICO LEGAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6049,28 +6049,32 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.235.755-0</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>15460.77</v>
+        <v>25098.81</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>256-1-CM25</t>
+          <t>1293138-148-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6085,7 +6089,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6095,12 +6099,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6110,12 +6114,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.610.398-5</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6129,13 +6133,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>25098.81</v>
+        <v>10736.19</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1293138-148-CM25</t>
+          <t>1293138-180-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6175,12 +6179,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
+          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>77.610.398-5</t>
+          <t>77.043.435-1</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6194,13 +6198,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>10736.19</v>
+        <v>13062.12</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1293138-180-CM25</t>
+          <t>1080157-88-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6215,7 +6219,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6225,27 +6229,27 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
+          <t>MADERERA LAGO VILLARRICA LIMITADA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>77.043.435-1</t>
+          <t>78.616.370-6</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6259,13 +6263,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>13062.12</v>
+        <v>5944.05</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1080157-88-CM25</t>
+          <t>4955-82-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6280,7 +6284,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6290,7 +6294,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6300,37 +6304,33 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>MADERERA LAGO VILLARRICA LIMITADA</t>
+          <t>MUEBLES EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>78.616.370-6</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.526.830-8</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>5944.05</v>
+        <v>9895.99</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4955-82-CM25</t>
+          <t>5178-3576-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>MUEBLES EASTON LIMITADA</t>
+          <t>INDUMAC LTDA.</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>79.526.830-8</t>
+          <t>83.732.700-8</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6385,13 +6385,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>9895.99</v>
+        <v>26818.71</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5178-3576-CM25</t>
+          <t>948354-1012-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.513.003-6</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6431,22 +6431,26 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>INDUMAC LTDA.</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>83.732.700-8</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>26818.71</v>
+        <v>43696.06</v>
       </c>
     </row>
     <row r="96">
@@ -6513,7 +6517,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>948354-1012-CM25</t>
+          <t>3179-256-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6528,7 +6532,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6538,12 +6542,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.513.003-6</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6572,13 +6576,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>43696.06</v>
+        <v>96349.89999999999</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3179-256-CM25</t>
+          <t>3179-237-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6593,7 +6597,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6637,13 +6641,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>96349.89999999999</v>
+        <v>10838.8</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>3179-237-CM25</t>
+          <t>1460278-50-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6658,22 +6662,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6683,32 +6687,28 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>ROMANESCU SPA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.199.251-K</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>10838.8</v>
+        <v>15119.37</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1460278-50-CM25</t>
+          <t>1079639-744-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6723,53 +6723,57 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>ROMANESCU SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>77.199.251-K</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>15119.37</v>
+        <v>28134.5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1079639-744-CM25</t>
+          <t>5510-108-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6784,37 +6788,37 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6828,13 +6832,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>28134.5</v>
+        <v>12216.86</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5510-108-CM25</t>
+          <t>3275-261-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6849,57 +6853,53 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.235.755-0</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>12216.86</v>
+        <v>14119.12</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1375158-3-CM25</t>
+          <t>3275-262-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6919,48 +6919,52 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.001.000-8</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO MEDICO LEGAL</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>MUEBLES EASTON LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>79.526.830-8</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>379344.16</v>
+        <v>21332.64</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3275-261-CM25</t>
+          <t>3275-263-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7015,13 +7019,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>14119.12</v>
+        <v>18024.74</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3275-262-CM25</t>
+          <t>5178-3868-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7036,7 +7040,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -7046,47 +7050,43 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>INDUMAC LTDA.</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>83.732.700-8</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>21332.64</v>
+        <v>9421.719999999999</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>3275-263-CM25</t>
+          <t>1293138-241-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -7111,43 +7111,47 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>76.235.755-0</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr"/>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>18024.74</v>
+        <v>43160.17</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>5178-3868-CM25</t>
+          <t>425-581-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7162,22 +7166,22 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7187,12 +7191,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>INDUMAC LTDA.</t>
+          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>83.732.700-8</t>
+          <t>76.235.755-0</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -7202,13 +7206,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>9421.719999999999</v>
+        <v>16532.07</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>425-581-CM25</t>
+          <t>867990-920-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7223,22 +7227,22 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7248,28 +7252,32 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>76.235.755-0</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>16532.07</v>
+        <v>5948.39</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1293138-241-CM25</t>
+          <t>1293138-243-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7284,7 +7292,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7309,26 +7317,22 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>COMERCIAL VYB SPA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.583.479-1</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>43160.17</v>
+        <v>32497.27</v>
       </c>
     </row>
     <row r="110">
@@ -7395,7 +7399,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1293138-243-CM25</t>
+          <t>2176-431-CM25</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7410,53 +7414,57 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>COMERCIAL VYB SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>76.583.479-1</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>32497.27</v>
+        <v>13466.75</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>867990-920-CM25</t>
+          <t>2173-201-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7471,22 +7479,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7496,32 +7504,28 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>5948.39</v>
+        <v>22722.3</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2176-431-CM25</t>
+          <t>1460278-90-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7531,62 +7535,58 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>ROMANESCU SPA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.199.251-K</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>13466.75</v>
+        <v>16893.15</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2173-201-CM25</t>
+          <t>1460278-88-CM25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7596,27 +7596,27 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>VENTURE STORE SPA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.733.054-5</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7641,13 +7641,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>22722.3</v>
+        <v>21043.95</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1460278-90-CM25</t>
+          <t>1075956-238-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7687,28 +7687,32 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>ROMANESCU SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>77.199.251-K</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>16893.15</v>
+        <v>11369.17</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1075956-238-CM25</t>
+          <t>5526-49-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7723,22 +7727,22 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7748,32 +7752,28 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>MUEBLES EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.526.830-8</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>11369.17</v>
+        <v>12939.53</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1460278-88-CM25</t>
+          <t>5872-164-CM25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7813,28 +7813,32 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>VENTURE STORE SPA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>76.733.054-5</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr"/>
+          <t>77.619.564-2</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>21043.95</v>
+        <v>5951.65</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>5526-49-CM25</t>
+          <t>3474-657-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7849,22 +7853,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7874,28 +7878,32 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>MUEBLES EASTON LIMITADA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>79.526.830-8</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>12939.53</v>
+        <v>15987.56</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>5872-164-CM25</t>
+          <t>5153-1984-CM25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7915,7 +7923,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7935,32 +7943,28 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>suria ltda</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.827.520-1</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>5951.65</v>
+        <v>18372.91</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>5153-1984-CM25</t>
+          <t>5684-439-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7975,7 +7979,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -8000,12 +8004,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>suria ltda</t>
+          <t>MUEBLES EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>77.827.520-1</t>
+          <t>79.526.830-8</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -8015,13 +8019,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>18372.91</v>
+        <v>43129.26</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3474-657-CM25</t>
+          <t>5531-228-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8036,7 +8040,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8046,12 +8050,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8061,12 +8065,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -8080,13 +8084,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>15987.56</v>
+        <v>48097.66</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>5684-439-CM25</t>
+          <t>1293138-256-CM25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8101,22 +8105,22 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8126,28 +8130,32 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>MUEBLES EASTON LIMITADA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>79.526.830-8</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr"/>
+          <t>77.619.564-2</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>43129.26</v>
+        <v>6852.76</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>5531-228-CM25</t>
+          <t>1075956-246-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8162,7 +8170,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8172,12 +8180,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8206,13 +8214,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>48097.66</v>
+        <v>17681.2</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1293138-256-CM25</t>
+          <t>4928-86-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8227,7 +8235,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -8237,12 +8245,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8252,12 +8260,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8271,13 +8279,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>6852.76</v>
+        <v>7072.04</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1075956-246-CM25</t>
+          <t>3173-57-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8292,7 +8300,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8302,7 +8310,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -8336,13 +8344,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>17681.2</v>
+        <v>12280.11</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>4928-86-CM25</t>
+          <t>3474-698-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8357,7 +8365,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8367,7 +8375,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -8382,32 +8390,28 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>INDUSTRIA DE CAMAS Y TEXTILES LIMITADA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.404.809-1</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>7072.04</v>
+        <v>20546.5</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3173-57-CM25</t>
+          <t>759-480-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8422,7 +8426,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8432,12 +8436,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.001.000-8</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8447,12 +8451,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.018.060-0</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8466,13 +8470,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>12280.11</v>
+        <v>9122.42</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>3474-698-CM25</t>
+          <t>2173-232-CM25</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8487,22 +8491,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8512,28 +8516,32 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>INDUSTRIA DE CAMAS Y TEXTILES LIMITADA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>76.404.809-1</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>20546.5</v>
+        <v>22838.74</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>759-480-CM25</t>
+          <t>1293138-270-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8543,12 +8551,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8558,12 +8566,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.001.000-8</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8573,12 +8581,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>GOOD HOSPITAL SPA</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>77.367.722-0</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -8592,13 +8600,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>9122.42</v>
+        <v>22850.61</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2173-232-CM25</t>
+          <t>1180842-38-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8608,12 +8616,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8623,47 +8631,43 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>92.999.000-5</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>22838.74</v>
+        <v>499470.96</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1293138-270-CM25</t>
+          <t>1293138-258-CM25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8678,7 +8682,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8703,12 +8707,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>GOOD HOSPITAL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>77.367.722-0</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -8722,13 +8726,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>22850.61</v>
+        <v>74498.05</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1180842-38-CM25</t>
+          <t>1293138-277-CM25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8743,53 +8747,57 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr"/>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>499470.96</v>
+        <v>8155</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1293138-258-CM25</t>
+          <t>1052231-109-CM25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8814,27 +8822,27 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8848,13 +8856,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>74498.05</v>
+        <v>5753.56</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1293138-277-CM25</t>
+          <t>1100335-54-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8879,12 +8887,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8894,12 +8902,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>IGMA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>76.465.697-0</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8913,13 +8921,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>8155</v>
+        <v>17525.41</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1052231-109-CM25</t>
+          <t>1293138-280-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8944,27 +8952,27 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>IGMA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>76.465.697-0</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8978,13 +8986,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>5753.56</v>
+        <v>20832.94</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1100335-54-CM25</t>
+          <t>5510-116-CM25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8999,22 +9007,22 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9024,32 +9032,28 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>IGMA CONSULTORES LIMITADA</t>
+          <t>MUEBLES EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>76.465.697-0</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.526.830-8</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>17525.41</v>
+        <v>55390.44</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1293138-280-CM25</t>
+          <t>5178-4585-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9064,7 +9068,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -9074,12 +9078,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9089,32 +9093,28 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>IGMA CONSULTORES LIMITADA</t>
+          <t>INDUMAC LTDA.</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>76.465.697-0</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>83.732.700-8</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>20832.94</v>
+        <v>16253.79</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>5178-4585-CM25</t>
+          <t>759-509-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9129,22 +9129,22 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.001.000-8</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9154,28 +9154,32 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>INDUMAC LTDA.</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>83.732.700-8</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>16253.79</v>
+        <v>410631.43</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5510-116-CM25</t>
+          <t>1293138-278-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9190,22 +9194,22 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9215,12 +9219,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>MUEBLES EASTON LIMITADA</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>79.526.830-8</t>
+          <t>92.999.000-5</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -9230,13 +9234,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>55390.44</v>
+        <v>13207.48</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>759-509-CM25</t>
+          <t>425-716-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9251,7 +9255,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -9261,12 +9265,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.001.000-8</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9276,12 +9280,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9295,13 +9299,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>410631.43</v>
+        <v>14960.08</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1293138-278-CM25</t>
+          <t>4180-152-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9316,7 +9320,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9326,43 +9330,47 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>13207.48</v>
+        <v>25899.08</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>4180-152-CM25</t>
+          <t>1057922-139-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9387,12 +9395,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9402,32 +9410,28 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MUEBLES EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.526.830-8</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>25899.08</v>
+        <v>111889.13</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>425-716-CM25</t>
+          <t>1057922-138-CM25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9447,52 +9451,48 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>MUEBLES EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.526.830-8</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>14960.08</v>
+        <v>131578.76</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1079576-4068-CM25</t>
+          <t>1293138-260-CM25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9517,47 +9517,43 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.533.330-4</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>18734.57</v>
+        <v>98730.73</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1293138-260-CM25</t>
+          <t>5153-2309-CM25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9577,17 +9573,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9597,12 +9593,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
+          <t>92.999.000-5</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9612,13 +9608,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>98730.73</v>
+        <v>151081.97</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5153-2309-CM25</t>
+          <t>1079566-464-CM25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9638,32 +9634,32 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.979.370-6</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>PEDRO ANTONIO PEDREROS CONCHA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
+          <t>10.595.925-7</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9673,13 +9669,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>151081.97</v>
+        <v>8347.959999999999</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1079566-464-CM25</t>
+          <t>1079576-4068-CM25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9704,7 +9700,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.979.370-6</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -9714,27 +9710,31 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO PEDREROS CONCHA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>10.595.925-7</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>8347.959999999999</v>
+        <v>18734.57</v>
       </c>
     </row>
     <row r="148">
@@ -10431,7 +10431,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5510-122-CM25</t>
+          <t>3290-337-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10451,48 +10451,52 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr"/>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>8757.98</v>
+        <v>12484.49</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1460278-223-CM25</t>
+          <t>5510-122-CM25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10512,17 +10516,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10532,12 +10536,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Econosillas</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>76.067.326-9</t>
+          <t>76.028.554-4</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10547,13 +10551,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>7120.29</v>
+        <v>8757.98</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>3290-337-CM25</t>
+          <t>1460278-223-CM25</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10578,41 +10582,37 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>Econosillas</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.067.326-9</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>12484.49</v>
+        <v>7120.29</v>
       </c>
     </row>
     <row r="162">
@@ -10809,7 +10809,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>5510-125-CM25</t>
+          <t>507428-3992-CM25</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10829,48 +10829,52 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>58232.68</v>
+        <v>61932.94</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1079580-493-CM25</t>
+          <t>5510-125-CM25</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10890,52 +10894,48 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>62.000.520-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.028.554-4</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>9425.889999999999</v>
+        <v>58232.68</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1079580-495-CM25</t>
+          <t>1079580-493-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10975,12 +10975,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -10994,13 +10994,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>17201.73</v>
+        <v>9425.889999999999</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>507428-3992-CM25</t>
+          <t>1079580-495-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11025,27 +11025,27 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>62.000.520-7</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>15.888.842-4</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -11059,7 +11059,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>61932.94</v>
+        <v>17201.73</v>
       </c>
     </row>
     <row r="169">
@@ -11768,7 +11768,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>948354-1689-CM25</t>
+          <t>2178-421-CM25</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11793,27 +11793,27 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.513.003-6</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>MUEBLES MELINA SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>77.472.821-K</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -11827,7 +11827,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>7596.26</v>
+        <v>13194.41</v>
       </c>
     </row>
     <row r="181">
@@ -11894,7 +11894,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2178-421-CM25</t>
+          <t>948354-1689-CM25</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11919,27 +11919,27 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.513.003-6</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>MUEBLES MELINA SPA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.472.821-K</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -11953,7 +11953,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>13194.41</v>
+        <v>7596.26</v>
       </c>
     </row>
     <row r="183">
@@ -12723,7 +12723,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1080936-6-CM26</t>
+          <t>5510-4-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12743,17 +12743,17 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>60.506.012-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12763,12 +12763,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>MUEBLES SANTIAGO SPA</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>76.369.344-9</t>
+          <t>76.028.554-4</t>
         </is>
       </c>
       <c r="K195" t="inlineStr"/>
@@ -12778,13 +12778,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>42194.91</v>
+        <v>27381.05</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>5510-4-CM26</t>
+          <t>1080936-5-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12804,17 +12804,17 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.506.012-9</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12824,12 +12824,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>MUNDO LOCKERS SPA</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
+          <t>76.580.205-9</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
@@ -12839,13 +12839,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>27381.05</v>
+        <v>49975.24</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1080936-5-CM26</t>
+          <t>1080936-6-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>MUNDO LOCKERS SPA</t>
+          <t>MUEBLES SANTIAGO SPA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>76.580.205-9</t>
+          <t>76.369.344-9</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -12900,13 +12900,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>49975.24</v>
+        <v>42194.91</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1475044-3-CM26</t>
+          <t>5153-79-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -12946,28 +12946,32 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr"/>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>15380.61</v>
+        <v>28936.33</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>5153-79-CM26</t>
+          <t>1475044-3-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12987,7 +12991,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -13007,26 +13011,22 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.028.554-4</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>28936.33</v>
+        <v>15380.61</v>
       </c>
     </row>
     <row r="200">
@@ -13276,7 +13276,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>5621-6-CM26</t>
+          <t>5153-163-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13316,32 +13316,28 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>92.999.000-5</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>111821.26</v>
+        <v>58655.43</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1080936-19-CM26</t>
+          <t>5647-21-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13366,12 +13362,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>60.506.012-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13381,12 +13377,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
+          <t>77.018.060-0</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -13400,13 +13396,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>17090.66</v>
+        <v>6886.7</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>5153-163-CM26</t>
+          <t>1080936-19-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13426,17 +13422,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.506.012-9</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13446,28 +13442,32 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr"/>
+          <t>15.888.842-4</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>58655.43</v>
+        <v>17090.66</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>5647-21-CM26</t>
+          <t>5621-6-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13487,7 +13487,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -13507,12 +13507,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -13526,7 +13526,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>6886.7</v>
+        <v>111821.26</v>
       </c>
     </row>
     <row r="208">
@@ -14670,7 +14670,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>5169-7-CM26</t>
+          <t>1475044-43-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14725,7 +14725,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>40957.09</v>
+        <v>37384.39</v>
       </c>
     </row>
     <row r="227">
@@ -14792,7 +14792,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1475044-43-CM26</t>
+          <t>5169-7-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>37384.39</v>
+        <v>40957.09</v>
       </c>
     </row>
     <row r="229">
@@ -15548,7 +15548,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>5067-897-CM26</t>
+          <t>1475044-45-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15573,12 +15573,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15588,12 +15588,12 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>MUEBLES TIMAUKEL LIMITADA</t>
+          <t>INTERGROUPE S.A.</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>78.042.830-9</t>
+          <t>76.719.470-6</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
@@ -15603,13 +15603,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>8913.08</v>
+        <v>66174.25</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1475044-45-CM26</t>
+          <t>5067-897-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15634,12 +15634,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15649,12 +15649,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>INTERGROUPE S.A.</t>
+          <t>MUEBLES TIMAUKEL LIMITADA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>76.719.470-6</t>
+          <t>78.042.830-9</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -15664,7 +15664,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>66174.25</v>
+        <v>8913.08</v>
       </c>
     </row>
     <row r="242">
@@ -15800,7 +15800,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>4794-54-CM26</t>
+          <t>1057922-24-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15815,53 +15815,57 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Articulos Deportivos Gacitua y Cia. Ltda</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>89.812.000-7</t>
-        </is>
-      </c>
-      <c r="K244" t="inlineStr"/>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>9691.6</v>
+        <v>39427.84</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>948354-749-CM26</t>
+          <t>4794-54-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15876,7 +15880,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -15886,12 +15890,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>61.513.003-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15901,32 +15905,28 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>IGMA CONSULTORES LIMITADA</t>
+          <t>Articulos Deportivos Gacitua y Cia. Ltda</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>76.465.697-0</t>
-        </is>
-      </c>
-      <c r="K245" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>89.812.000-7</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>5672.37</v>
+        <v>9691.6</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2175-173-CM26</t>
+          <t>948354-749-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15941,47 +15941,51 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.513.003-6</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>IGMA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K246" t="inlineStr"/>
+          <t>76.465.697-0</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>6548.16</v>
+        <v>5672.37</v>
       </c>
     </row>
     <row r="247">
@@ -16048,7 +16052,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>5153-829-CM26</t>
+          <t>2175-173-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16063,7 +16067,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -16073,47 +16077,43 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>23008.02</v>
+        <v>6548.16</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2177-50-CM26</t>
+          <t>5153-829-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16138,27 +16138,27 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -16172,13 +16172,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>12279.86</v>
+        <v>23008.02</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1475044-49-CM26</t>
+          <t>2177-50-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16193,47 +16193,51 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>INTERGROUPE S.A.</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>76.719.470-6</t>
-        </is>
-      </c>
-      <c r="K250" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>14910.91</v>
+        <v>12279.86</v>
       </c>
     </row>
     <row r="251">
@@ -16304,7 +16308,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2176-246-CM26</t>
+          <t>1475044-49-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16319,37 +16323,37 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>INTERGROUPE S.A.</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.719.470-6</t>
         </is>
       </c>
       <c r="K252" t="inlineStr"/>
@@ -16359,13 +16363,13 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>19186.66</v>
+        <v>14910.91</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1524816-10-CM26</t>
+          <t>2176-246-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -16380,57 +16384,53 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K253" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>9080.32</v>
+        <v>19186.66</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>5178-2120-CM26</t>
+          <t>1524816-10-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16445,7 +16445,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -16489,13 +16489,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>28336.43</v>
+        <v>9080.32</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2173-112-CM26</t>
+          <t>5178-2120-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16510,22 +16510,22 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16535,22 +16535,26 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K255" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>106898.33</v>
+        <v>28336.43</v>
       </c>
     </row>
     <row r="256">
@@ -16617,7 +16621,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>3179-148-CM26</t>
+          <t>2173-112-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16632,7 +16636,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -16642,12 +16646,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16672,13 +16676,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>17163.91</v>
+        <v>106898.33</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>5510-54-CM26</t>
+          <t>3179-148-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16693,7 +16697,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -16703,12 +16707,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16718,32 +16722,28 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>31782.04</v>
+        <v>17163.91</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>5510-55-CM26</t>
+          <t>5510-54-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16802,13 +16802,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>27411.55</v>
+        <v>31782.04</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1293138-132-CM26</t>
+          <t>5510-55-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16818,12 +16818,12 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -16833,12 +16833,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16848,28 +16848,32 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>77.749.210-1</t>
-        </is>
-      </c>
-      <c r="K260" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>8700.799999999999</v>
+        <v>27411.55</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1460278-208-CM26</t>
+          <t>1293138-132-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16884,22 +16888,22 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16909,32 +16913,28 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
-        </is>
-      </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.749.210-1</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr"/>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>6178.09</v>
+        <v>8700.799999999999</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>4642-586-CM26</t>
+          <t>1460278-208-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16949,7 +16949,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -16959,12 +16959,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>60.514.000-9</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16974,22 +16974,26 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr"/>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>12904.77</v>
+        <v>6178.09</v>
       </c>
     </row>
     <row r="263">
@@ -17056,7 +17060,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>5153-1058-CM26</t>
+          <t>4642-586-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -17071,22 +17075,22 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.514.000-9</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -17096,12 +17100,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K264" t="inlineStr"/>
@@ -17111,13 +17115,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>59033.55</v>
+        <v>12904.77</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>5520-3737-CM26</t>
+          <t>5153-1058-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17132,12 +17136,12 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -17157,32 +17161,28 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>92.999.000-5</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>6791.69</v>
+        <v>59033.55</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>5647-107-CM26</t>
+          <t>1057922-25-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17202,48 +17202,52 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
-        </is>
-      </c>
-      <c r="K266" t="inlineStr"/>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>15280.06</v>
+        <v>7637.44</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2178-186-CM26</t>
+          <t>5520-3737-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17258,7 +17262,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -17268,27 +17272,27 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -17302,13 +17306,13 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>21833.41</v>
+        <v>6791.69</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>4794-75-CM26</t>
+          <t>5647-107-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17323,7 +17327,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -17348,12 +17352,12 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>INTERGROUPE S.A.</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>76.719.470-6</t>
+          <t>76.028.554-4</t>
         </is>
       </c>
       <c r="K268" t="inlineStr"/>
@@ -17363,13 +17367,13 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>14693.99</v>
+        <v>15280.06</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1698-174-CM26</t>
+          <t>2178-186-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17379,17 +17383,17 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -17404,33 +17408,37 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>6540.55</v>
+        <v>21833.41</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>5178-2904-CM26</t>
+          <t>4794-75-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17440,12 +17448,12 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -17470,32 +17478,28 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>INTERGROUPE S.A.</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.719.470-6</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr"/>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>10087.86</v>
+        <v>14693.99</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>793-13-CM26</t>
+          <t>1698-174-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -17510,7 +17514,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -17520,27 +17524,27 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>INTERGROUPE S.A.</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>76.719.470-6</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K271" t="inlineStr"/>
@@ -17550,13 +17554,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>17139.53</v>
+        <v>6540.55</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1460278-272-CM26</t>
+          <t>5178-2904-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17571,22 +17575,22 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17596,12 +17600,12 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -17615,13 +17619,13 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>25566.37</v>
+        <v>10087.86</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>5510-63-CM26</t>
+          <t>793-13-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17636,7 +17640,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -17661,12 +17665,12 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>INTERGROUPE S.A.</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
+          <t>76.719.470-6</t>
         </is>
       </c>
       <c r="K273" t="inlineStr"/>
@@ -17676,13 +17680,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>51211.49</v>
+        <v>17139.53</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>5510-64-CM26</t>
+          <t>1460278-272-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17697,7 +17701,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -17707,12 +17711,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17722,28 +17726,32 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
-        </is>
-      </c>
-      <c r="K274" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>54648.37</v>
+        <v>25566.37</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>5510-65-CM26</t>
+          <t>5510-64-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17758,7 +17766,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -17798,13 +17806,13 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>63478.5</v>
+        <v>54648.37</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>5510-66-CM26</t>
+          <t>5510-63-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17819,7 +17827,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -17859,13 +17867,13 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>38661.76</v>
+        <v>51211.49</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>5520-4160-CM26</t>
+          <t>5510-66-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -17880,12 +17888,12 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -17905,12 +17913,12 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>Econosillas</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>76.067.326-9</t>
+          <t>76.028.554-4</t>
         </is>
       </c>
       <c r="K277" t="inlineStr"/>
@@ -17920,13 +17928,13 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>8675.530000000001</v>
+        <v>38661.76</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>507428-711-CM26</t>
+          <t>5510-65-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17941,7 +17949,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -17951,47 +17959,43 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>GOOD HOSPITAL SPA</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>77.367.722-0</t>
-        </is>
-      </c>
-      <c r="K278" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.028.554-4</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>8918.309999999999</v>
+        <v>63478.5</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1460278-299-CM26</t>
+          <t>5520-4160-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -18006,22 +18010,22 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -18031,32 +18035,28 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>Econosillas</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K279" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.067.326-9</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>7728.65</v>
+        <v>8675.530000000001</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>5647-80-CM26</t>
+          <t>507428-711-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18071,7 +18071,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -18081,43 +18081,47 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>CHILESEATING</t>
+          <t>GOOD HOSPITAL SPA</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>76.675.854-1</t>
-        </is>
-      </c>
-      <c r="K280" t="inlineStr"/>
+          <t>77.367.722-0</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>198848.63</v>
+        <v>8918.309999999999</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>5510-67-CM26</t>
+          <t>1460278-299-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18132,7 +18136,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -18142,12 +18146,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -18157,28 +18161,32 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
-        </is>
-      </c>
-      <c r="K281" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>63182.31</v>
+        <v>7728.65</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>705829-35-CM26</t>
+          <t>5510-67-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18193,7 +18201,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -18218,12 +18226,12 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>INTERGROUPE S.A.</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>76.719.470-6</t>
+          <t>76.028.554-4</t>
         </is>
       </c>
       <c r="K282" t="inlineStr"/>
@@ -18233,13 +18241,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>20839.69</v>
+        <v>63182.31</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>5533-9-CM26</t>
+          <t>5647-80-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18254,7 +18262,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -18279,12 +18287,12 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>INTERGROUPE S.A.</t>
+          <t>CHILESEATING</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>76.719.470-6</t>
+          <t>76.675.854-1</t>
         </is>
       </c>
       <c r="K283" t="inlineStr"/>
@@ -18294,13 +18302,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>38626.39</v>
+        <v>198848.63</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>3434-68-CM26</t>
+          <t>5533-9-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18315,7 +18323,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -18325,27 +18333,27 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
+          <t>INTERGROUPE S.A.</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>11.216.890-7</t>
+          <t>76.719.470-6</t>
         </is>
       </c>
       <c r="K284" t="inlineStr"/>
@@ -18355,13 +18363,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>22822.53</v>
+        <v>38626.39</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>3179-224-CM26</t>
+          <t>705829-35-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18376,7 +18384,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -18386,12 +18394,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18401,12 +18409,12 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>INTERGROUPE S.A.</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.719.470-6</t>
         </is>
       </c>
       <c r="K285" t="inlineStr"/>
@@ -18416,13 +18424,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>6323.67</v>
+        <v>20839.69</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>3179-216-CM26</t>
+          <t>3434-68-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18432,22 +18440,22 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -18457,37 +18465,33 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>11.216.890-7</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr"/>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>9528.299999999999</v>
+        <v>22822.53</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>948354-1260-CM26</t>
+          <t>3179-224-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -18497,12 +18501,12 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -18512,12 +18516,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>61.513.003-6</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -18527,32 +18531,28 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
-        </is>
-      </c>
-      <c r="K287" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr"/>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>10154.26</v>
+        <v>6323.67</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>759-265-CM26</t>
+          <t>3179-216-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -18567,7 +18567,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -18577,12 +18577,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>61.001.000-8</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -18611,13 +18611,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>9919.450000000001</v>
+        <v>9528.299999999999</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>5153-1382-CM26</t>
+          <t>948354-1260-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18632,7 +18632,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -18642,12 +18642,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.513.003-6</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18657,12 +18657,12 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>77.018.060-0</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -18676,13 +18676,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>16760.75</v>
+        <v>10154.26</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1460278-335-CM26</t>
+          <t>759-265-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18697,7 +18697,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -18707,12 +18707,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>61.001.000-8</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18722,28 +18722,32 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>CHILESEATING</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>76.675.854-1</t>
-        </is>
-      </c>
-      <c r="K290" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>10906.78</v>
+        <v>9919.450000000001</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>5067-1772-CM26</t>
+          <t>5153-1382-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18758,7 +18762,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -18768,12 +18772,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18783,28 +18787,32 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>CHILESEATING</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>76.675.854-1</t>
-        </is>
-      </c>
-      <c r="K291" t="inlineStr"/>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>68935.75999999999</v>
+        <v>16760.75</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>507428-878-CM26</t>
+          <t>1460278-335-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18819,37 +18827,37 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
+          <t>CHILESEATING</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>77.749.210-1</t>
+          <t>76.675.854-1</t>
         </is>
       </c>
       <c r="K292" t="inlineStr"/>
@@ -18859,13 +18867,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>55525</v>
+        <v>10906.78</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>3474-469-CM26</t>
+          <t>5067-1772-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18880,7 +18888,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -18890,12 +18898,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18905,32 +18913,28 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>CHILESEATING</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
-        </is>
-      </c>
-      <c r="K293" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.675.854-1</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr"/>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>11047.36</v>
+        <v>68935.75999999999</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>3179-253-CM26</t>
+          <t>3474-469-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18945,7 +18949,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -18955,7 +18959,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -18970,12 +18974,12 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.018.060-0</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -18989,13 +18993,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>71052.28</v>
+        <v>11047.36</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>948354-1407-CM26</t>
+          <t>507428-878-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -19005,12 +19009,12 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -19020,27 +19024,27 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>61.513.003-6</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>TAZ S A</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>96.891.420-0</t>
+          <t>77.749.210-1</t>
         </is>
       </c>
       <c r="K295" t="inlineStr"/>
@@ -19050,13 +19054,13 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>11095.48</v>
+        <v>55525</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>507428-898-CM26</t>
+          <t>3179-253-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -19066,12 +19070,12 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -19081,43 +19085,47 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>77.749.210-1</t>
-        </is>
-      </c>
-      <c r="K296" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>13119.84</v>
+        <v>71052.28</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>507428-915-CM26</t>
+          <t>948354-1407-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19132,7 +19140,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -19142,27 +19150,27 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>61.513.003-6</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
+          <t>TAZ S A</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>77.749.210-1</t>
+          <t>96.891.420-0</t>
         </is>
       </c>
       <c r="K297" t="inlineStr"/>
@@ -19172,13 +19180,13 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>22190.26</v>
+        <v>11095.48</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>507428-935-CM26</t>
+          <t>507428-915-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19193,7 +19201,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -19233,13 +19241,13 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>18683.27</v>
+        <v>22190.26</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>507428-891-CM26</t>
+          <t>507428-898-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19254,7 +19262,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -19279,12 +19287,12 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>Plusmedical SpA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>76.520.087-3</t>
+          <t>77.749.210-1</t>
         </is>
       </c>
       <c r="K299" t="inlineStr"/>
@@ -19294,13 +19302,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>29443</v>
+        <v>13119.84</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>5647-164-CM26</t>
+          <t>507428-935-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19315,7 +19323,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -19325,27 +19333,27 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
+          <t>77.749.210-1</t>
         </is>
       </c>
       <c r="K300" t="inlineStr"/>
@@ -19355,13 +19363,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>10832.95</v>
+        <v>18683.27</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>3474-519-CM26</t>
+          <t>507428-891-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19376,7 +19384,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -19386,27 +19394,27 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>CHILESEATING</t>
+          <t>Plusmedical SpA</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>76.675.854-1</t>
+          <t>76.520.087-3</t>
         </is>
       </c>
       <c r="K301" t="inlineStr"/>
@@ -19416,13 +19424,13 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>31726.47</v>
+        <v>29443</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2173-239-CM26</t>
+          <t>5647-164-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -19437,22 +19445,22 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -19462,12 +19470,12 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.028.554-4</t>
         </is>
       </c>
       <c r="K302" t="inlineStr"/>
@@ -19477,72 +19485,686 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>9571.030000000001</v>
+        <v>10832.95</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
+          <t>3474-519-CM26</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>61.979.960-7</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>CHILESEATING</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>76.675.854-1</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr"/>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M303" s="2" t="n">
+        <v>31726.47</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2173-239-CM26</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M304" s="2" t="n">
+        <v>9571.030000000001</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
           <t>5510-92-CM26</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr">
+      <c r="B305" t="inlineStr">
         <is>
           <t>2239-4-LR25</t>
         </is>
       </c>
-      <c r="C303" t="inlineStr">
+      <c r="C305" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr">
+      <c r="D305" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="E303" t="inlineStr">
+      <c r="E305" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F303" t="inlineStr">
+      <c r="F305" t="inlineStr">
         <is>
           <t>60.910.000-1</t>
         </is>
       </c>
-      <c r="G303" t="inlineStr">
+      <c r="G305" t="inlineStr">
         <is>
           <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
-      <c r="H303" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I303" t="inlineStr">
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
         <is>
           <t>EVENTAIL SPA</t>
         </is>
       </c>
-      <c r="J303" t="inlineStr">
+      <c r="J305" t="inlineStr">
         <is>
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L303" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M303" s="2" t="n">
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M305" s="2" t="n">
         <v>9259.51</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>5441-489-CM26</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>EASTON LIMITADA</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>76.028.554-4</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr"/>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M306" s="2" t="n">
+        <v>37378.86</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>4794-103-CM26</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>INTERGROUPE S.A.</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>76.719.470-6</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr"/>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M307" s="2" t="n">
+        <v>25721.1</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>1057922-69-CM26</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>61.607.600-0</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD OSORNO</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>EASTON LIMITADA</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>76.028.554-4</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr"/>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M308" s="2" t="n">
+        <v>149242.35</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>5640-57-CM26</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>INTERGROUPE S.A.</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>76.719.470-6</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr"/>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M309" s="2" t="n">
+        <v>58487.38</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>5640-56-CM26</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>INTERGROUPE S.A.</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>76.719.470-6</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr"/>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M310" s="2" t="n">
+        <v>58999.19</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>1475044-78-CM26</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>INTERGROUPE S.A.</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>76.719.470-6</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr"/>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M311" s="2" t="n">
+        <v>60463.1</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>4794-104-CM26</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>INTERGROUPE S.A.</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>76.719.470-6</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr"/>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M312" s="2" t="n">
+        <v>60771.52</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>5529-105-CM26</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M313" s="2" t="n">
+        <v>7994.81</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-top-organismos/mobiliario-general-escolar-y-clinico.xlsx
+++ b/docs/oc-top-organismos/mobiliario-general-escolar-y-clinico.xlsx
@@ -669,7 +669,11 @@
           <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
@@ -795,7 +799,11 @@
           <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>MUEBLES ANDROMEDA DOS SPA</t>
@@ -1043,7 +1051,11 @@
           <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>JAIME DEIK Y CIA. LIMITADA</t>
@@ -15820,7 +15832,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -16702,7 +16714,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -16893,7 +16905,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -17645,7 +17657,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -18076,7 +18088,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -18389,7 +18401,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -18450,7 +18462,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -18511,7 +18523,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -18893,7 +18905,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">

--- a/docs/oc-top-organismos/mobiliario-general-escolar-y-clinico.xlsx
+++ b/docs/oc-top-organismos/mobiliario-general-escolar-y-clinico.xlsx
@@ -19523,7 +19523,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
